--- a/datos_06.diccionario-datos.xlsx
+++ b/datos_06.diccionario-datos.xlsx
@@ -500,15 +500,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="B2:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -519,18 +518,17 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Estudio de demanda potencial para un Doctorado en Ciencias</t>
+          <t>Datos y Scripts de Procesamiento para el Artículo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>orientado al paisaje y turismo rural, desarrollo, manejo y aprovechamiento del paisaje rural</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t>"Demanda Potencial para un Doctorado en Ciencias en Paisaje y Rurismo Rural"</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -539,161 +537,182 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Universidad Autónoma Metropolitana (UAM), Ciudad de México</t>
+          <t>Colegio de Postgraduados, Campus Córdoba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Instrumento</t>
+          <t>Responsable del proyecto de investigación</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Cuestionario de demanda potencial para Doctorado en Ciencias (Google Forms)</t>
+          <t>Dra. Obdulia Baltazar Bernal (obduliabb@colpos.mx)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Periodo de levantamiento</t>
+          <t>Responsable del repositorio y sus productos</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>4 de abril de 2024 – 7 de mayo de 2024</t>
+          <t>Dr. Jesús Zavala Ruiz (jzr@xanum.uam.mx)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Unidad de observación</t>
+          <t>Instrumento</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Persona egresada o estudiante de maestría, respondiente individual</t>
+          <t>Cuestionario de demanda potencial para Doctorado en Ciencias (Google Forms)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>N total de respuestas</t>
+          <t>Periodo de levantamiento</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>4 de abril de 2024 – 7 de mayo de 2024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>N con interés declarado ('Sí')</t>
+          <t>Unidad de observación</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Persona egresada o estudiante de maestría, respondiente individual</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Archivos relacionados</t>
+          <t>N total de respuestas</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>datos_01.datos-brutos-cuestionario.* · datos_04.datos-limpios-completos.* · datos_05.datos-interesados.* · datos_03.limpieza-datos.R</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Licencia sugerida</t>
+          <t>N con interés declarado ('Sí')</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>CC BY 4.0 (coherente con acceso abierto de RIDE, Iniciativa de Budapest)</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>Archivos relacionados</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>datos_01.datos-brutos-cuestionario.* · datos_04.datos-limpios-completos.* · datos_05.datos-interesados.* · datos_03.limpieza-datos.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Licencia sugerida</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>CC BY 4.0 (coherente con acceso abierto de RIDE, https://www.ride.org.mx/, Iniciativa de Budapest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>Última actualización de este diccionario</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>22 de julio de 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>26 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Cómo usar este archivo:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>• Hoja 'Variables': catálogo completo de las 13 variables del dataset (nombre, tipo, pregunta de origen, valores válidos).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>• Hoja 'Codebook_Recodificacion': mapeo valor crudo -&gt; valor limpio para cada variable recodificada, con la regla aplicada.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>• Hoja 'Calidad_Datos': hallazgos de la auditoría de limpieza (issues, severidad, variable afectada, recomendación).</t>
+          <t>• Hoja 'Variables': catálogo completo de las 13 variables del dataset (nombre, tipo, pregunta de origen, valores válidos).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
+          <t>• Hoja 'Codebook_Recodificacion': mapeo valor crudo -&gt; valor limpio para cada variable recodificada, con la regla aplicada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>• Hoja 'Calidad_Datos': hallazgos de la auditoría de limpieza (issues, severidad, variable afectada, recomendación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
           <t>• Hoja 'Estadisticas_Descriptivas': frecuencias y porcentajes por variable, listas para citar en el artículo.</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23">
-      <c r="B23" s="6" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Actualización 2 (v3):</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>A partir del 22 de julio de 2026, la limpieza se rehizo en 2 pasos siguiendo lineamientos del equipo: (1) estandarización explícita de acentos/entidades vía catálogo auditable y uso de NA real para dato faltante, preservando en columnas '_otro_texto' toda respuesta libre que no encaja en categorías; (2) automatización completa en 01_limpieza_datos_v2.R, exportando a csv, xlsx y rds. Ver hoja 'Codebook_v3_2pasos'.</t>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>A partir del 22 de julio de 2026, la limpieza se rehizo en 2 pasos siguiendo lineamientos del equipo: (1) estandarización explícita de acentos/entidades vía catálogo auditable y uso de NA real para dato faltante, preservando en columnas '_otro_texto' toda respuesta libre que no encaja en categorías; (2) automatización completa en datos_03.limpieza-datos.R, exportando a csv, xlsx y rds. Ver hoja 'Codebook_v3_2pasos'.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
